--- a/ExperimentSummarySheet_Ex1.xlsx
+++ b/ExperimentSummarySheet_Ex1.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25.42" customWidth="1" style="2" min="1" max="1"/>
@@ -530,312 +530,414 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Vasilis &amp; Riccardo</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Multinomial Naive Bayes</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Bag-of-Words (counts)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>lowercase + punctuation + stopwords removed (sentiment words kept: no/not/nor/up/down)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>none (priors learned from data)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>alpha=1.0 (Laplace), fit_prior=True</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>0.66</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Errors mostly = confusions with neutral majority, not polarity flips; positives understated as neutral reporting</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>baseline; macro-F1 &lt;&lt; accuracy reveals minority-class neglect</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Vasilis &amp; Riccardo</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Multinomial Naive Bayes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>TF-IDF</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>same (text_stopwords)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>alpha=1.0, fit_prior=True</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.68</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Collapsed to neutral; negative recall 0.06. TF-IDF flattens likelihoods -&gt; prior dominates</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>accuracy barely moved (0.68) but macro-F1 cratered (0.45): macro-F1 is the honest metric</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Vasilis &amp; Riccardo</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Multinomial Naive Bayes</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Bag-of-Words</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>same (text_stopwords)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>uniform prior (fit_prior=False) to counter 59/28/12 imbalance</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>alpha=1.0, fit_prior=False</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.68</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>0.64</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>More balanced: negative recall 0.53-&gt;0.63; sacrifices some neutral accuracy</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>class-imbalance handling; model stops defaulting to majority</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Vasilis &amp; Riccardo</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Feed-forward NN (sklearn MLPClassifier)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Bag-of-Words</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>same (text_stopwords)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>hidden_layer_sizes=(100,), ReLU, Adam, max_iter=200, random_state=42 (~876K params)</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>0.67</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Same error pattern as NB (collapses to neutral); slightly more balanced per-class</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>~876K params barely beat NB (0.67 vs 0.66): word presence nearly sufficient</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Vasilis &amp; Riccardo</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Feed-forward NN (MLPClassifier)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>TF-IDF</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>same (text_stopwords)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>hidden_layer_sizes=(100,), max_iter=200, random_state=42</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.71</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Negative recall 0.54 (vs NB's 0.06 on TF-IDF): NN robust to TF-IDF because it has no prior</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>KEY: representation effects interact with classifier; TF-IDF only breaks NB</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Vasilis &amp; Riccardo</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>NB &amp; NN (BINARY, neutral removed)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Bag-of-Words</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>same (text_stopwords); 1967 rows (pos 1363 / neg 604)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>stratified split</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>NB alpha=1.0; NN (100,) max_iter=200</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>NB 0.84 / NN 0.86</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>NB 0.81 / NN 0.83</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Negative recall jumps (NB 0.53-&gt;0.70, NN 0.57-&gt;0.74); removing neutral deletes the dominant error mode</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Difficulty lived in separating sentiment from neutrality, not pos vs neg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vasilis &amp; Riccardo</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DistilBERT (distilbert-base-uncased), fine-tuned</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Contextual subword embeddings (transformer)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAW text (no cleaning) — model's own WordPiece tokenizer; max_length=128</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>stratified split (no extra handling needed)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3 epochs, batch=16, lr=2e-5, max_length=128, seed=42; ran on Colab T4 GPU (~61s)</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Fixes Task 3 failures: negative recall 0.53-&gt;0.89, positive-&gt;neutral confusion 109-&gt;50; handles negation/domain knowledge/implicit sentiment</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>MULTICLASS. macro-F1 0.66/0.67 (NB/NN) -&gt; 0.82. Converged in 1-2 epochs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vasilis &amp; Riccardo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DistilBERT, fine-tuned (BINARY, neutral removed)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Contextual subword embeddings</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAW text; max_length=128; 1967 rows (pos 1363 / neg 604)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>stratified split</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3 epochs, batch=16, lr=2e-5, seed=42; Colab T4 GPU</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Only 18 errors / 394; negative recall 0.95 (was 0.53 in Task 3). Val F1 flat after epoch 1-2 -&gt; mild overfitting onset</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>BINARY. macro-F1 0.81/0.83 (NB/NN) -&gt; 0.95. Near ceiling. Cost: needs GPU vs classical models' seconds on CPU; no interpretability</t>
         </is>
       </c>
     </row>

--- a/ExperimentSummarySheet_Ex1.xlsx
+++ b/ExperimentSummarySheet_Ex1.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Errors mostly = confusions with neutral majority, not polarity flips; positives understated as neutral reporting</t>
+          <t>Mostly confused with neutral majority, not polarity flips.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Collapsed to neutral; negative recall 0.06. TF-IDF flattens likelihoods -&gt; prior dominates</t>
+          <t>Collapses to neutral; negative recall 0.06 (TF-IDF flattens likelihoods, prior dominates).</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>More balanced: negative recall 0.53-&gt;0.63; sacrifices some neutral accuracy</t>
+          <t>More balanced; negative recall 0.53-&gt;0.63, small neutral-accuracy loss.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Same error pattern as NB (collapses to neutral); slightly more balanced per-class</t>
+          <t>Same neutral-collapse pattern as NB; slightly more balanced per class.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Negative recall 0.54 (vs NB's 0.06 on TF-IDF): NN robust to TF-IDF because it has no prior</t>
+          <t>Negative recall 0.54 (vs NB 0.06): NN unaffected by TF-IDF (no prior).</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Negative recall jumps (NB 0.53-&gt;0.70, NN 0.57-&gt;0.74); removing neutral deletes the dominant error mode</t>
+          <t>Negative recall jumps (NB 0.53-&gt;0.70, NN 0.57-&gt;0.74); neutral was the dominant error.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,102 +840,102 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Vasilis &amp; Riccardo</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>DistilBERT (distilbert-base-uncased), fine-tuned</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Contextual subword embeddings (transformer)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>RAW text (no cleaning) — model's own WordPiece tokenizer; max_length=128</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>stratified split (no extra handling needed)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3 epochs, batch=16, lr=2e-5, max_length=128, seed=42; ran on Colab T4 GPU (~61s)</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="2" t="n">
         <v>0.82</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Fixes Task 3 failures: negative recall 0.53-&gt;0.89, positive-&gt;neutral confusion 109-&gt;50; handles negation/domain knowledge/implicit sentiment</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Fixes Task 3 failures: negative recall 0.53-&gt;0.86; positive-&gt;neutral confusion 109-&gt;50.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MULTICLASS. macro-F1 0.66/0.67 (NB/NN) -&gt; 0.82. Converged in 1-2 epochs</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Vasilis &amp; Riccardo</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>DistilBERT, fine-tuned (BINARY, neutral removed)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Contextual subword embeddings</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>RAW text; max_length=128; 1967 rows (pos 1363 / neg 604)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>stratified split</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>3 epochs, batch=16, lr=2e-5, seed=42; Colab T4 GPU</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Only 18 errors / 394; negative recall 0.95 (was 0.53 in Task 3). Val F1 flat after epoch 1-2 -&gt; mild overfitting onset</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Only 18 errors/394; negative recall 0.95. Converges in 1-2 epochs.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>BINARY. macro-F1 0.81/0.83 (NB/NN) -&gt; 0.95. Near ceiling. Cost: needs GPU vs classical models' seconds on CPU; no interpretability</t>
         </is>

--- a/ExperimentSummarySheet_Ex1.xlsx
+++ b/ExperimentSummarySheet_Ex1.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Class Handlning</t>
+          <t>Class Handling</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0.82</v>
